--- a/artfynd/A 49753-2019 artfynd.xlsx
+++ b/artfynd/A 49753-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 49753-2019 artfynd.xlsx
+++ b/artfynd/A 49753-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY158"/>
+  <dimension ref="A1:AY155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3464,7 +3464,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>80563524</v>
+        <v>92297479</v>
       </c>
       <c r="B24" t="n">
         <v>90699</v>
@@ -3504,13 +3504,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>542293.9508567556</v>
+        <v>542292.9832558802</v>
       </c>
       <c r="R24" t="n">
-        <v>6756790.482508794</v>
+        <v>6756789.984993835</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2019-10-12</t>
+          <t>2020-05-26</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2019-10-12</t>
+          <t>2020-05-26</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
@@ -3552,11 +3552,6 @@
           <t>00:00</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Skogen är avverkningsanmäld</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3565,26 +3560,16 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>Tallnaturskog</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>silverlåga tall</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -11191,7 +11176,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>80563532</v>
+        <v>92297480</v>
       </c>
       <c r="B85" t="n">
         <v>90699</v>
@@ -11231,13 +11216,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>542356.2708834074</v>
+        <v>542355.7899850487</v>
       </c>
       <c r="R85" t="n">
-        <v>6756789.281345225</v>
+        <v>6756788.789618123</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -11261,7 +11246,7 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2019-10-12</t>
+          <t>2020-05-26</t>
         </is>
       </c>
       <c r="Z85" t="inlineStr">
@@ -11271,7 +11256,7 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2019-10-12</t>
+          <t>2020-05-26</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
@@ -11279,11 +11264,6 @@
           <t>00:00</t>
         </is>
       </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Skogen är avverkningsanmäld</t>
-        </is>
-      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
@@ -11292,26 +11272,16 @@
       </c>
       <c r="AG85" t="b">
         <v>0</v>
-      </c>
-      <c r="AI85" t="inlineStr">
-        <is>
-          <t>Tallnaturskog</t>
-        </is>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>silverlåga tall</t>
-        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -14097,10 +14067,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>80563533</v>
+        <v>80563471</v>
       </c>
       <c r="B108" t="n">
-        <v>77506</v>
+        <v>89633</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -14109,25 +14079,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -14137,10 +14107,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>542351.8152941181</v>
+        <v>541992.9703942286</v>
       </c>
       <c r="R108" t="n">
-        <v>6756795.546079519</v>
+        <v>6756721.787235428</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -14206,7 +14176,7 @@
       </c>
       <c r="AO108" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>silverlåga tall</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr"/>
@@ -14224,10 +14194,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>80563471</v>
+        <v>80563465</v>
       </c>
       <c r="B109" t="n">
-        <v>89633</v>
+        <v>77595</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -14236,25 +14206,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>65</v>
+        <v>6450</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -14264,10 +14234,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>541992.9703942286</v>
+        <v>541984.3591053768</v>
       </c>
       <c r="R109" t="n">
-        <v>6756721.787235428</v>
+        <v>6756709.049423062</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -14333,7 +14303,7 @@
       </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>silverlåga tall</t>
+          <t>mossigt block</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -14351,10 +14321,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>80563465</v>
+        <v>80563516</v>
       </c>
       <c r="B110" t="n">
-        <v>77595</v>
+        <v>77258</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -14363,25 +14333,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6450</v>
+        <v>6446</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -14391,10 +14361,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>541984.3591053768</v>
+        <v>542214.2254392838</v>
       </c>
       <c r="R110" t="n">
-        <v>6756709.049423062</v>
+        <v>6756781.757991372</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -14460,7 +14430,7 @@
       </c>
       <c r="AO110" t="inlineStr">
         <is>
-          <t>mossigt block</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr"/>
@@ -14478,10 +14448,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>80563516</v>
+        <v>80563408</v>
       </c>
       <c r="B111" t="n">
-        <v>77258</v>
+        <v>77506</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -14494,21 +14464,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -14518,10 +14488,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>542214.2254392838</v>
+        <v>542375.8056995753</v>
       </c>
       <c r="R111" t="n">
-        <v>6756781.757991372</v>
+        <v>6756416.739783907</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -14587,7 +14557,7 @@
       </c>
       <c r="AO111" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AT111" t="inlineStr"/>
@@ -14605,10 +14575,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>80563408</v>
+        <v>80563490</v>
       </c>
       <c r="B112" t="n">
-        <v>77506</v>
+        <v>89545</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -14617,25 +14587,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -14645,10 +14615,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>542375.8056995753</v>
+        <v>542059.6462432086</v>
       </c>
       <c r="R112" t="n">
-        <v>6756416.739783907</v>
+        <v>6756763.885996817</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -14714,7 +14684,7 @@
       </c>
       <c r="AO112" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>silverlåga tall</t>
         </is>
       </c>
       <c r="AT112" t="inlineStr"/>
@@ -14732,10 +14702,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>80563490</v>
+        <v>80563496</v>
       </c>
       <c r="B113" t="n">
-        <v>89545</v>
+        <v>88476</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -14744,25 +14714,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1503</v>
+        <v>1962</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -14772,10 +14742,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>542059.6462432086</v>
+        <v>542079.8887543216</v>
       </c>
       <c r="R113" t="n">
-        <v>6756763.885996817</v>
+        <v>6756739.826059321</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -14859,10 +14829,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>80563496</v>
+        <v>80563501</v>
       </c>
       <c r="B114" t="n">
-        <v>88476</v>
+        <v>89406</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -14875,21 +14845,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1962</v>
+        <v>1204</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -14899,10 +14869,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>542079.8887543216</v>
+        <v>542100.5288434718</v>
       </c>
       <c r="R114" t="n">
-        <v>6756739.826059321</v>
+        <v>6756764.370455828</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -14986,10 +14956,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>80563501</v>
+        <v>80563375</v>
       </c>
       <c r="B115" t="n">
-        <v>89406</v>
+        <v>88476</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -15002,21 +14972,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1204</v>
+        <v>1962</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -15026,10 +14996,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>542100.5288434718</v>
+        <v>542393.2364453404</v>
       </c>
       <c r="R115" t="n">
-        <v>6756764.370455828</v>
+        <v>6756791.666422527</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -15113,10 +15083,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>80563375</v>
+        <v>80563409</v>
       </c>
       <c r="B116" t="n">
-        <v>88476</v>
+        <v>77506</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -15129,21 +15099,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -15153,10 +15123,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>542393.2364453404</v>
+        <v>542349.5678073646</v>
       </c>
       <c r="R116" t="n">
-        <v>6756791.666422527</v>
+        <v>6756412.53848017</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -15222,7 +15192,7 @@
       </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>silverlåga tall</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -15240,7 +15210,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>80563409</v>
+        <v>80563468</v>
       </c>
       <c r="B117" t="n">
         <v>77506</v>
@@ -15280,10 +15250,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>542349.5678073646</v>
+        <v>541972.0651219523</v>
       </c>
       <c r="R117" t="n">
-        <v>6756412.53848017</v>
+        <v>6756719.596090375</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -15367,10 +15337,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>80563468</v>
+        <v>80563473</v>
       </c>
       <c r="B118" t="n">
-        <v>77506</v>
+        <v>77595</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -15379,25 +15349,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -15407,10 +15377,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>541972.0651219523</v>
+        <v>541972.8375055759</v>
       </c>
       <c r="R118" t="n">
-        <v>6756719.596090375</v>
+        <v>6756736.615146243</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -15476,7 +15446,7 @@
       </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>mossigt block</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -15494,10 +15464,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>80563473</v>
+        <v>80563417</v>
       </c>
       <c r="B119" t="n">
-        <v>77595</v>
+        <v>77506</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -15506,25 +15476,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -15534,10 +15504,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>541972.8375055759</v>
+        <v>542273.6585712427</v>
       </c>
       <c r="R119" t="n">
-        <v>6756736.615146243</v>
+        <v>6756409.689954374</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -15603,7 +15573,7 @@
       </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>mossigt block</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -15621,10 +15591,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>80563417</v>
+        <v>80563434</v>
       </c>
       <c r="B120" t="n">
-        <v>77506</v>
+        <v>88476</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -15637,21 +15607,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -15661,10 +15631,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>542273.6585712427</v>
+        <v>542239.0628214276</v>
       </c>
       <c r="R120" t="n">
-        <v>6756409.689954374</v>
+        <v>6756535.161084728</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -15730,7 +15700,7 @@
       </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>silverlåga tall</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -15748,10 +15718,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>80563434</v>
+        <v>80563395</v>
       </c>
       <c r="B121" t="n">
-        <v>88476</v>
+        <v>79433</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -15764,21 +15734,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1962</v>
+        <v>1049</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -15788,10 +15758,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>542239.0628214276</v>
+        <v>542385.9853801366</v>
       </c>
       <c r="R121" t="n">
-        <v>6756535.161084728</v>
+        <v>6756542.743888739</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -15857,7 +15827,7 @@
       </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>silverlåga tall</t>
+          <t>högstubbe silverved tall</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -15875,10 +15845,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>80563395</v>
+        <v>80563371</v>
       </c>
       <c r="B122" t="n">
-        <v>79433</v>
+        <v>77506</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -15891,21 +15861,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -15915,10 +15885,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>542385.9853801366</v>
+        <v>542416.974168502</v>
       </c>
       <c r="R122" t="n">
-        <v>6756542.743888739</v>
+        <v>6756801.183704589</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -15984,7 +15954,7 @@
       </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>högstubbe silverved tall</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>
@@ -16002,7 +15972,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>80563371</v>
+        <v>80563531</v>
       </c>
       <c r="B123" t="n">
         <v>77506</v>
@@ -16042,10 +16012,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>542416.974168502</v>
+        <v>542349.0168288364</v>
       </c>
       <c r="R123" t="n">
-        <v>6756801.183704589</v>
+        <v>6756785.306897092</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -16129,7 +16099,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>80563531</v>
+        <v>80563512</v>
       </c>
       <c r="B124" t="n">
         <v>77506</v>
@@ -16169,10 +16139,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>542349.0168288364</v>
+        <v>542215.545433604</v>
       </c>
       <c r="R124" t="n">
-        <v>6756785.306897092</v>
+        <v>6756752.614074546</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -16256,10 +16226,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>80563512</v>
+        <v>80563374</v>
       </c>
       <c r="B125" t="n">
-        <v>77506</v>
+        <v>90841</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -16272,21 +16242,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -16296,10 +16266,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>542215.545433604</v>
+        <v>542396.1159990114</v>
       </c>
       <c r="R125" t="n">
-        <v>6756752.614074546</v>
+        <v>6756795.102734809</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -16365,7 +16335,7 @@
       </c>
       <c r="AO125" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>silverlåga tall</t>
         </is>
       </c>
       <c r="AT125" t="inlineStr"/>
@@ -16383,10 +16353,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>80563374</v>
+        <v>80563406</v>
       </c>
       <c r="B126" t="n">
-        <v>90841</v>
+        <v>77506</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -16399,21 +16369,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -16423,10 +16393,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>542396.1159990114</v>
+        <v>542380.3020075599</v>
       </c>
       <c r="R126" t="n">
-        <v>6756795.102734809</v>
+        <v>6756447.899980617</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -16492,7 +16462,7 @@
       </c>
       <c r="AO126" t="inlineStr">
         <is>
-          <t>silverlåga tall</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AT126" t="inlineStr"/>
@@ -16510,7 +16480,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>80563406</v>
+        <v>80563436</v>
       </c>
       <c r="B127" t="n">
         <v>77506</v>
@@ -16550,10 +16520,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>542380.3020075599</v>
+        <v>542209.2279517013</v>
       </c>
       <c r="R127" t="n">
-        <v>6756447.899980617</v>
+        <v>6756546.956969103</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -16637,10 +16607,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>80563436</v>
+        <v>80563398</v>
       </c>
       <c r="B128" t="n">
-        <v>77506</v>
+        <v>79433</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -16653,21 +16623,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -16677,10 +16647,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>542209.2279517013</v>
+        <v>542382.4453213658</v>
       </c>
       <c r="R128" t="n">
-        <v>6756546.956969103</v>
+        <v>6756513.054007756</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -16746,7 +16716,7 @@
       </c>
       <c r="AO128" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>högstubbe silverved tall</t>
         </is>
       </c>
       <c r="AT128" t="inlineStr"/>
@@ -16764,10 +16734,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>80563398</v>
+        <v>80563462</v>
       </c>
       <c r="B129" t="n">
-        <v>79433</v>
+        <v>88476</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -16780,21 +16750,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1049</v>
+        <v>1962</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -16804,10 +16774,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>542382.4453213658</v>
+        <v>541974.6035382819</v>
       </c>
       <c r="R129" t="n">
-        <v>6756513.054007756</v>
+        <v>6756669.567838169</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -16873,7 +16843,7 @@
       </c>
       <c r="AO129" t="inlineStr">
         <is>
-          <t>högstubbe silverved tall</t>
+          <t>silverlåga tall</t>
         </is>
       </c>
       <c r="AT129" t="inlineStr"/>
@@ -16891,7 +16861,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>80563462</v>
+        <v>80563535</v>
       </c>
       <c r="B130" t="n">
         <v>88476</v>
@@ -16931,10 +16901,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>541974.6035382819</v>
+        <v>542358.9649892664</v>
       </c>
       <c r="R130" t="n">
-        <v>6756669.567838169</v>
+        <v>6756808.267080042</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -17018,10 +16988,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>80563535</v>
+        <v>80563435</v>
       </c>
       <c r="B131" t="n">
-        <v>88476</v>
+        <v>77177</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -17034,21 +17004,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -17058,10 +17028,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>542358.9649892664</v>
+        <v>542235.9864018587</v>
       </c>
       <c r="R131" t="n">
-        <v>6756808.267080042</v>
+        <v>6756548.247152288</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -17145,10 +17115,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>80563435</v>
+        <v>80563455</v>
       </c>
       <c r="B132" t="n">
-        <v>77177</v>
+        <v>88476</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -17161,21 +17131,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>353</v>
+        <v>1962</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -17185,10 +17155,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>542235.9864018587</v>
+        <v>542109.4399938117</v>
       </c>
       <c r="R132" t="n">
-        <v>6756548.247152288</v>
+        <v>6756587.570106697</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -17272,10 +17242,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>80563455</v>
+        <v>80563400</v>
       </c>
       <c r="B133" t="n">
-        <v>88476</v>
+        <v>90653</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -17284,25 +17254,25 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -17312,10 +17282,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>542109.4399938117</v>
+        <v>542394.7470519276</v>
       </c>
       <c r="R133" t="n">
-        <v>6756587.570106697</v>
+        <v>6756502.022158651</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -17377,11 +17347,6 @@
       <c r="AI133" t="inlineStr">
         <is>
           <t>Tallnaturskog</t>
-        </is>
-      </c>
-      <c r="AO133" t="inlineStr">
-        <is>
-          <t>silverlåga tall</t>
         </is>
       </c>
       <c r="AT133" t="inlineStr"/>
@@ -17399,10 +17364,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>80563400</v>
+        <v>80563428</v>
       </c>
       <c r="B134" t="n">
-        <v>90653</v>
+        <v>89406</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -17411,25 +17376,25 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>4364</v>
+        <v>1204</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -17439,10 +17404,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>542394.7470519276</v>
+        <v>542180.7400085548</v>
       </c>
       <c r="R134" t="n">
-        <v>6756502.022158651</v>
+        <v>6756486.351076975</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -17504,6 +17469,11 @@
       <c r="AI134" t="inlineStr">
         <is>
           <t>Tallnaturskog</t>
+        </is>
+      </c>
+      <c r="AO134" t="inlineStr">
+        <is>
+          <t>silverlåga tall</t>
         </is>
       </c>
       <c r="AT134" t="inlineStr"/>
@@ -17521,10 +17491,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>80563428</v>
+        <v>80563542</v>
       </c>
       <c r="B135" t="n">
-        <v>89406</v>
+        <v>77506</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -17537,21 +17507,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -17561,10 +17531,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>542180.7400085548</v>
+        <v>542374.2372112334</v>
       </c>
       <c r="R135" t="n">
-        <v>6756486.351076975</v>
+        <v>6756874.543107799</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -17630,7 +17600,7 @@
       </c>
       <c r="AO135" t="inlineStr">
         <is>
-          <t>silverlåga tall</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AT135" t="inlineStr"/>
@@ -17648,7 +17618,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>80563542</v>
+        <v>80563405</v>
       </c>
       <c r="B136" t="n">
         <v>77506</v>
@@ -17688,10 +17658,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>542374.2372112334</v>
+        <v>542379.1951484102</v>
       </c>
       <c r="R136" t="n">
-        <v>6756874.543107799</v>
+        <v>6756459.065620723</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -17775,10 +17745,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>80563405</v>
+        <v>80563514</v>
       </c>
       <c r="B137" t="n">
-        <v>77506</v>
+        <v>79433</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -17791,21 +17761,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -17815,10 +17785,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>542379.1951484102</v>
+        <v>542226.525720727</v>
       </c>
       <c r="R137" t="n">
-        <v>6756459.065620723</v>
+        <v>6756770.726414197</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -17884,7 +17854,7 @@
       </c>
       <c r="AO137" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>högstubbe silverved tall</t>
         </is>
       </c>
       <c r="AT137" t="inlineStr"/>
@@ -17902,10 +17872,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>80563514</v>
+        <v>80563460</v>
       </c>
       <c r="B138" t="n">
-        <v>79433</v>
+        <v>90841</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -17918,21 +17888,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1049</v>
+        <v>2079</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -17942,10 +17912,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>542226.525720727</v>
+        <v>541998.3201727943</v>
       </c>
       <c r="R138" t="n">
-        <v>6756770.726414197</v>
+        <v>6756681.026364577</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -18011,7 +17981,7 @@
       </c>
       <c r="AO138" t="inlineStr">
         <is>
-          <t>högstubbe silverved tall</t>
+          <t>silverlåga tall</t>
         </is>
       </c>
       <c r="AT138" t="inlineStr"/>
@@ -18029,10 +17999,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>80563460</v>
+        <v>80563526</v>
       </c>
       <c r="B139" t="n">
-        <v>90841</v>
+        <v>77506</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -18045,21 +18015,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -18069,10 +18039,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>541998.3201727943</v>
+        <v>542323.1988347718</v>
       </c>
       <c r="R139" t="n">
-        <v>6756681.026364577</v>
+        <v>6756786.943055314</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -18138,7 +18108,7 @@
       </c>
       <c r="AO139" t="inlineStr">
         <is>
-          <t>silverlåga tall</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AT139" t="inlineStr"/>
@@ -18156,10 +18126,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>80563526</v>
+        <v>80563444</v>
       </c>
       <c r="B140" t="n">
-        <v>77506</v>
+        <v>79433</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -18172,21 +18142,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -18196,10 +18166,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>542323.1988347718</v>
+        <v>542152.4019638423</v>
       </c>
       <c r="R140" t="n">
-        <v>6756786.943055314</v>
+        <v>6756536.075517706</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -18265,7 +18235,7 @@
       </c>
       <c r="AO140" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>högstubbe silverved tall</t>
         </is>
       </c>
       <c r="AT140" t="inlineStr"/>
@@ -18283,10 +18253,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>80563444</v>
+        <v>80563509</v>
       </c>
       <c r="B141" t="n">
-        <v>79433</v>
+        <v>77506</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -18299,21 +18269,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -18323,10 +18293,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>542152.4019638423</v>
+        <v>542199.6402704417</v>
       </c>
       <c r="R141" t="n">
-        <v>6756536.075517706</v>
+        <v>6756739.303127049</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -18392,7 +18362,7 @@
       </c>
       <c r="AO141" t="inlineStr">
         <is>
-          <t>högstubbe silverved tall</t>
+          <t>äldre tall</t>
         </is>
       </c>
       <c r="AT141" t="inlineStr"/>
@@ -18410,7 +18380,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>80563509</v>
+        <v>80563370</v>
       </c>
       <c r="B142" t="n">
         <v>77506</v>
@@ -18450,10 +18420,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>542199.6402704417</v>
+        <v>542410.4092214302</v>
       </c>
       <c r="R142" t="n">
-        <v>6756739.303127049</v>
+        <v>6756821.030809661</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -18519,7 +18489,7 @@
       </c>
       <c r="AO142" t="inlineStr">
         <is>
-          <t>äldre tall</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AT142" t="inlineStr"/>
@@ -18537,10 +18507,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>80563370</v>
+        <v>80563450</v>
       </c>
       <c r="B143" t="n">
-        <v>77506</v>
+        <v>77259</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -18553,21 +18523,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -18577,10 +18547,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>542410.4092214302</v>
+        <v>542122.7486376907</v>
       </c>
       <c r="R143" t="n">
-        <v>6756821.030809661</v>
+        <v>6756573.633400314</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -18646,7 +18616,7 @@
       </c>
       <c r="AO143" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT143" t="inlineStr"/>
@@ -18664,10 +18634,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>80563450</v>
+        <v>80563402</v>
       </c>
       <c r="B144" t="n">
-        <v>77259</v>
+        <v>77177</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -18680,21 +18650,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -18704,10 +18674,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>542122.7486376907</v>
+        <v>542378.7950193848</v>
       </c>
       <c r="R144" t="n">
-        <v>6756573.633400314</v>
+        <v>6756492.597180375</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -18773,7 +18743,7 @@
       </c>
       <c r="AO144" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>silverlåga tall</t>
         </is>
       </c>
       <c r="AT144" t="inlineStr"/>
@@ -18791,10 +18761,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>80563402</v>
+        <v>80563373</v>
       </c>
       <c r="B145" t="n">
-        <v>77177</v>
+        <v>78098</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -18807,21 +18777,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -18831,10 +18801,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>542378.7950193848</v>
+        <v>542414.0540122131</v>
       </c>
       <c r="R145" t="n">
-        <v>6756492.597180375</v>
+        <v>6756801.148824423</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -18900,7 +18870,7 @@
       </c>
       <c r="AO145" t="inlineStr">
         <is>
-          <t>silverlåga tall</t>
+          <t>dimensionsstubbe tall</t>
         </is>
       </c>
       <c r="AT145" t="inlineStr"/>
@@ -18918,7 +18888,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>80563373</v>
+        <v>80563540</v>
       </c>
       <c r="B146" t="n">
         <v>78098</v>
@@ -18958,10 +18928,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>542414.0540122131</v>
+        <v>542365.1467672029</v>
       </c>
       <c r="R146" t="n">
-        <v>6756801.148824423</v>
+        <v>6756861.313171737</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -19045,10 +19015,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>80563540</v>
+        <v>80563422</v>
       </c>
       <c r="B147" t="n">
-        <v>78098</v>
+        <v>89545</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -19057,25 +19027,25 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -19085,10 +19055,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>542365.1467672029</v>
+        <v>542254.926204699</v>
       </c>
       <c r="R147" t="n">
-        <v>6756861.313171737</v>
+        <v>6756470.221817243</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -19154,7 +19124,7 @@
       </c>
       <c r="AO147" t="inlineStr">
         <is>
-          <t>dimensionsstubbe tall</t>
+          <t>silverlåga tall</t>
         </is>
       </c>
       <c r="AT147" t="inlineStr"/>
@@ -19172,10 +19142,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>80563422</v>
+        <v>80563466</v>
       </c>
       <c r="B148" t="n">
-        <v>89545</v>
+        <v>88476</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -19184,25 +19154,25 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1503</v>
+        <v>1962</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -19212,10 +19182,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>542254.926204699</v>
+        <v>541975.3329967514</v>
       </c>
       <c r="R148" t="n">
-        <v>6756470.221817243</v>
+        <v>6756607.853176943</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -19299,10 +19269,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>80563466</v>
+        <v>80563507</v>
       </c>
       <c r="B149" t="n">
-        <v>88476</v>
+        <v>77506</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -19315,21 +19285,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -19339,10 +19309,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>541975.3329967514</v>
+        <v>542179.5527735153</v>
       </c>
       <c r="R149" t="n">
-        <v>6756607.853176943</v>
+        <v>6756750.242390563</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -19408,7 +19378,7 @@
       </c>
       <c r="AO149" t="inlineStr">
         <is>
-          <t>silverlåga tall</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AT149" t="inlineStr"/>
@@ -19426,7 +19396,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>80563507</v>
+        <v>80563381</v>
       </c>
       <c r="B150" t="n">
         <v>77506</v>
@@ -19466,10 +19436,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>542179.5527735153</v>
+        <v>542398.2381156201</v>
       </c>
       <c r="R150" t="n">
-        <v>6756750.242390563</v>
+        <v>6756698.90068119</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -19553,10 +19523,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>80563381</v>
+        <v>88280481</v>
       </c>
       <c r="B151" t="n">
-        <v>77506</v>
+        <v>89412</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -19569,34 +19539,34 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Stora Björnberget, Dlr</t>
+          <t>Stora Björnberget, söder om toppen, nyckelbiotop, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>542398.2381156201</v>
+        <v>542006.7858861716</v>
       </c>
       <c r="R151" t="n">
-        <v>6756698.90068119</v>
+        <v>6756747.222486209</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -19623,7 +19593,7 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>2019-10-12</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="Z151" t="inlineStr">
@@ -19633,7 +19603,7 @@
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2019-10-12</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="AB151" t="inlineStr">
@@ -19643,7 +19613,7 @@
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>Skogen är avverkningsanmäld</t>
+          <t>En fk</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -19657,33 +19627,37 @@
       </c>
       <c r="AI151" t="inlineStr">
         <is>
-          <t>Tallnaturskog</t>
+          <t>Naturskogsartad äldre tallskog</t>
         </is>
       </c>
       <c r="AO151" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>Tall 27 cm</t>
         </is>
       </c>
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lars-Ove Wikars</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY151" t="inlineStr"/>
+          <t>Lars-Ove Wikars, Rolf Lundqvist</t>
+        </is>
+      </c>
+      <c r="AY151" t="inlineStr">
+        <is>
+          <t>Insekter på tallved i Dalarna 2020 - 2021</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>88280481</v>
+        <v>92297580</v>
       </c>
       <c r="B152" t="n">
-        <v>89412</v>
+        <v>77259</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -19696,37 +19670,37 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>5442</v>
+        <v>228912</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Stora Björnberget, söder om toppen, nyckelbiotop, Dlr</t>
+          <t>Stora Björnberget, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>542006.7858861716</v>
+        <v>541997.184065572</v>
       </c>
       <c r="R152" t="n">
-        <v>6756747.222486209</v>
+        <v>6756735.931004629</v>
       </c>
       <c r="S152" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -19750,7 +19724,7 @@
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2020-08-25</t>
         </is>
       </c>
       <c r="Z152" t="inlineStr">
@@ -19760,7 +19734,7 @@
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2020-08-25</t>
         </is>
       </c>
       <c r="AB152" t="inlineStr">
@@ -19768,11 +19742,6 @@
           <t>00:00</t>
         </is>
       </c>
-      <c r="AC152" t="inlineStr">
-        <is>
-          <t>En fk</t>
-        </is>
-      </c>
       <c r="AD152" t="b">
         <v>0</v>
       </c>
@@ -19781,40 +19750,26 @@
       </c>
       <c r="AG152" t="b">
         <v>0</v>
-      </c>
-      <c r="AI152" t="inlineStr">
-        <is>
-          <t>Naturskogsartad äldre tallskog</t>
-        </is>
-      </c>
-      <c r="AO152" t="inlineStr">
-        <is>
-          <t>Tall 27 cm</t>
-        </is>
       </c>
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Lars-Ove Wikars</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Lars-Ove Wikars, Rolf Lundqvist</t>
-        </is>
-      </c>
-      <c r="AY152" t="inlineStr">
-        <is>
-          <t>Insekter på tallved i Dalarna 2020 - 2021</t>
-        </is>
-      </c>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>92297479</v>
+        <v>92297581</v>
       </c>
       <c r="B153" t="n">
-        <v>90699</v>
+        <v>77258</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -19823,25 +19778,25 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>232140</v>
+        <v>6446</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -19851,10 +19806,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>542292.9832558802</v>
+        <v>541997.184065572</v>
       </c>
       <c r="R153" t="n">
-        <v>6756789.984993835</v>
+        <v>6756735.931004629</v>
       </c>
       <c r="S153" t="n">
         <v>5</v>
@@ -19881,7 +19836,7 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>2020-05-26</t>
+          <t>2020-08-25</t>
         </is>
       </c>
       <c r="Z153" t="inlineStr">
@@ -19891,7 +19846,7 @@
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2020-05-26</t>
+          <t>2020-08-25</t>
         </is>
       </c>
       <c r="AB153" t="inlineStr">
@@ -19923,10 +19878,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>92297580</v>
+        <v>92297478</v>
       </c>
       <c r="B154" t="n">
-        <v>77259</v>
+        <v>57150</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -19935,25 +19890,25 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>228912</v>
+        <v>208260</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Vipera berus</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -19963,10 +19918,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>541997.184065572</v>
+        <v>542278.2262254546</v>
       </c>
       <c r="R154" t="n">
-        <v>6756735.931004629</v>
+        <v>6756802.930990207</v>
       </c>
       <c r="S154" t="n">
         <v>5</v>
@@ -19993,7 +19948,7 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>2020-08-25</t>
+          <t>2020-05-26</t>
         </is>
       </c>
       <c r="Z154" t="inlineStr">
@@ -20003,7 +19958,7 @@
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2020-08-25</t>
+          <t>2020-05-26</t>
         </is>
       </c>
       <c r="AB154" t="inlineStr">
@@ -20035,10 +19990,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>92297480</v>
+        <v>108964154</v>
       </c>
       <c r="B155" t="n">
-        <v>90699</v>
+        <v>77787</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -20047,41 +20002,42 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>232140</v>
+        <v>967</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
           <t>Stora Björnberget, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>542355.7899850487</v>
+        <v>542106</v>
       </c>
       <c r="R155" t="n">
-        <v>6756788.789618123</v>
+        <v>6756745</v>
       </c>
       <c r="S155" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -20105,22 +20061,22 @@
       </c>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>2020-05-26</t>
+          <t>2023-05-11</t>
         </is>
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2020-05-26</t>
+          <t>2023-05-11</t>
         </is>
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -20135,352 +20091,15 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Pär Karlsson</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Pär Karlsson</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
-    </row>
-    <row r="156">
-      <c r="A156" t="n">
-        <v>92297581</v>
-      </c>
-      <c r="B156" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E156" t="n">
-        <v>6446</v>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>Kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>Carbonicola anthracophila</t>
-        </is>
-      </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr"/>
-      <c r="P156" t="inlineStr">
-        <is>
-          <t>Stora Björnberget, Dlr</t>
-        </is>
-      </c>
-      <c r="Q156" t="n">
-        <v>541997.184065572</v>
-      </c>
-      <c r="R156" t="n">
-        <v>6756735.931004629</v>
-      </c>
-      <c r="S156" t="n">
-        <v>5</v>
-      </c>
-      <c r="T156" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U156" t="inlineStr">
-        <is>
-          <t>Falun</t>
-        </is>
-      </c>
-      <c r="V156" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W156" t="inlineStr">
-        <is>
-          <t>Enviken</t>
-        </is>
-      </c>
-      <c r="Y156" t="inlineStr">
-        <is>
-          <t>2020-08-25</t>
-        </is>
-      </c>
-      <c r="Z156" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA156" t="inlineStr">
-        <is>
-          <t>2020-08-25</t>
-        </is>
-      </c>
-      <c r="AB156" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD156" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE156" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG156" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT156" t="inlineStr"/>
-      <c r="AW156" t="inlineStr">
-        <is>
-          <t>Uno Skog</t>
-        </is>
-      </c>
-      <c r="AX156" t="inlineStr">
-        <is>
-          <t>Uno Skog</t>
-        </is>
-      </c>
-      <c r="AY156" t="inlineStr"/>
-    </row>
-    <row r="157">
-      <c r="A157" t="n">
-        <v>92297478</v>
-      </c>
-      <c r="B157" t="n">
-        <v>57150</v>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E157" t="n">
-        <v>208260</v>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>Huggorm</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>Vipera berus</t>
-        </is>
-      </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr"/>
-      <c r="P157" t="inlineStr">
-        <is>
-          <t>Stora Björnberget, Dlr</t>
-        </is>
-      </c>
-      <c r="Q157" t="n">
-        <v>542278.2262254546</v>
-      </c>
-      <c r="R157" t="n">
-        <v>6756802.930990207</v>
-      </c>
-      <c r="S157" t="n">
-        <v>5</v>
-      </c>
-      <c r="T157" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U157" t="inlineStr">
-        <is>
-          <t>Falun</t>
-        </is>
-      </c>
-      <c r="V157" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W157" t="inlineStr">
-        <is>
-          <t>Enviken</t>
-        </is>
-      </c>
-      <c r="Y157" t="inlineStr">
-        <is>
-          <t>2020-05-26</t>
-        </is>
-      </c>
-      <c r="Z157" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA157" t="inlineStr">
-        <is>
-          <t>2020-05-26</t>
-        </is>
-      </c>
-      <c r="AB157" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD157" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE157" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG157" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT157" t="inlineStr"/>
-      <c r="AW157" t="inlineStr">
-        <is>
-          <t>Uno Skog</t>
-        </is>
-      </c>
-      <c r="AX157" t="inlineStr">
-        <is>
-          <t>Uno Skog</t>
-        </is>
-      </c>
-      <c r="AY157" t="inlineStr"/>
-    </row>
-    <row r="158">
-      <c r="A158" t="n">
-        <v>108964154</v>
-      </c>
-      <c r="B158" t="n">
-        <v>77787</v>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E158" t="n">
-        <v>967</v>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>Varglav</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>Letharia vulpina</t>
-        </is>
-      </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>(L.) Hue</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr"/>
-      <c r="K158" t="inlineStr"/>
-      <c r="P158" t="inlineStr">
-        <is>
-          <t>Stora Björnberget, Dlr</t>
-        </is>
-      </c>
-      <c r="Q158" t="n">
-        <v>542106</v>
-      </c>
-      <c r="R158" t="n">
-        <v>6756745</v>
-      </c>
-      <c r="S158" t="n">
-        <v>25</v>
-      </c>
-      <c r="T158" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U158" t="inlineStr">
-        <is>
-          <t>Falun</t>
-        </is>
-      </c>
-      <c r="V158" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W158" t="inlineStr">
-        <is>
-          <t>Enviken</t>
-        </is>
-      </c>
-      <c r="Y158" t="inlineStr">
-        <is>
-          <t>2023-05-11</t>
-        </is>
-      </c>
-      <c r="Z158" t="inlineStr">
-        <is>
-          <t>10:57</t>
-        </is>
-      </c>
-      <c r="AA158" t="inlineStr">
-        <is>
-          <t>2023-05-11</t>
-        </is>
-      </c>
-      <c r="AB158" t="inlineStr">
-        <is>
-          <t>10:57</t>
-        </is>
-      </c>
-      <c r="AD158" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE158" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG158" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT158" t="inlineStr"/>
-      <c r="AW158" t="inlineStr">
-        <is>
-          <t>Pär Karlsson</t>
-        </is>
-      </c>
-      <c r="AX158" t="inlineStr">
-        <is>
-          <t>Pär Karlsson</t>
-        </is>
-      </c>
-      <c r="AY158" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49753-2019 artfynd.xlsx
+++ b/artfynd/A 49753-2019 artfynd.xlsx
@@ -20103,10 +20103,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>126983336</v>
+        <v>126975570</v>
       </c>
       <c r="B156" t="n">
-        <v>79075</v>
+        <v>91339</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -20114,37 +20114,46 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>967</v>
+        <v>5442</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P156" t="inlineStr">
         <is>
           <t>Stora Björnberget, Stora Björnberget, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>542115</v>
+        <v>542077</v>
       </c>
       <c r="R156" t="n">
-        <v>6756691</v>
+        <v>6756768</v>
       </c>
       <c r="S156" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -20173,7 +20182,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -20183,7 +20192,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -20210,10 +20219,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>126975570</v>
+        <v>126983336</v>
       </c>
       <c r="B157" t="n">
-        <v>91265</v>
+        <v>79106</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -20221,46 +20230,37 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>5442</v>
+        <v>967</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J157" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) Hue</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
           <t>Stora Björnberget, Stora Björnberget, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>542077</v>
+        <v>542115</v>
       </c>
       <c r="R157" t="n">
-        <v>6756768</v>
+        <v>6756691</v>
       </c>
       <c r="S157" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -20289,7 +20289,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -20299,7 +20299,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -20326,10 +20326,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>126975579</v>
+        <v>126976219</v>
       </c>
       <c r="B158" t="n">
-        <v>78980</v>
+        <v>79106</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -20337,21 +20337,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6425</v>
+        <v>967</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -20361,10 +20361,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>542064</v>
+        <v>542082</v>
       </c>
       <c r="R158" t="n">
-        <v>6756762</v>
+        <v>6756663</v>
       </c>
       <c r="S158" t="n">
         <v>7</v>
@@ -20396,7 +20396,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -20406,7 +20406,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -20417,6 +20417,26 @@
       </c>
       <c r="AG158" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ158" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK158" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM158" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO158" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
@@ -20433,10 +20453,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>126976219</v>
+        <v>126975579</v>
       </c>
       <c r="B159" t="n">
-        <v>79075</v>
+        <v>79011</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -20444,21 +20464,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>967</v>
+        <v>6425</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -20468,10 +20488,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>542082</v>
+        <v>542064</v>
       </c>
       <c r="R159" t="n">
-        <v>6756663</v>
+        <v>6756762</v>
       </c>
       <c r="S159" t="n">
         <v>7</v>
@@ -20503,7 +20523,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -20513,7 +20533,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -20524,26 +20544,6 @@
       </c>
       <c r="AG159" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ159" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK159" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM159" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO159" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
